--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -32,10 +32,10 @@
     <t>Negativo</t>
   </si>
   <si>
-    <t>Non idoneo</t>
+    <t>Positivo</t>
   </si>
   <si>
-    <t>Positivo</t>
+    <t>Non idoneo</t>
   </si>
 </sst>
 </file>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -32,10 +32,10 @@
     <t>Negativo</t>
   </si>
   <si>
-    <t>Positivo</t>
+    <t>Non idoneo</t>
   </si>
   <si>
-    <t>Non idoneo</t>
+    <t>Positivo</t>
   </si>
 </sst>
 </file>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
   <si>
     <t>Area</t>
   </si>
@@ -36,6 +36,30 @@
   </si>
   <si>
     <t>Positivo</t>
+  </si>
+  <si>
+    <t>La</t>
+  </si>
+  <si>
+    <t>INF</t>
+  </si>
+  <si>
+    <t>LIM</t>
+  </si>
+  <si>
+    <t>Lazio</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Viterbo</t>
+  </si>
+  <si>
+    <t>Cinghiale</t>
+  </si>
+  <si>
+    <t>Suino</t>
   </si>
 </sst>
 </file>
@@ -110,14 +134,134 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2"/>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1674.0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2276.0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>93.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
